--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/122.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/122.xlsx
@@ -426,13 +426,13 @@
         <v>-18.33966684368922</v>
       </c>
       <c r="E2">
-        <v>-18.2321320352553</v>
+        <v>-11.55626923856968</v>
       </c>
       <c r="F2">
-        <v>0.2673496334342131</v>
+        <v>0.6413459186545507</v>
       </c>
       <c r="G2">
-        <v>-15.11927886006825</v>
+        <v>-12.14163099747102</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.12372773675549</v>
       </c>
       <c r="E3">
-        <v>-19.75371741572857</v>
+        <v>-13.30787845626257</v>
       </c>
       <c r="F3">
-        <v>0.3562823294313652</v>
+        <v>0.6237837013477984</v>
       </c>
       <c r="G3">
-        <v>-14.82041207554778</v>
+        <v>-10.78223731150087</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.79706607248338</v>
       </c>
       <c r="E4">
-        <v>-19.93913125549862</v>
+        <v>-13.17267633628956</v>
       </c>
       <c r="F4">
-        <v>0.2063155231959455</v>
+        <v>0.5066392967135035</v>
       </c>
       <c r="G4">
-        <v>-14.4388519452862</v>
+        <v>-10.75567910419872</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.38736487454148</v>
       </c>
       <c r="E5">
-        <v>-20.12579042562079</v>
+        <v>-13.91982473434108</v>
       </c>
       <c r="F5">
-        <v>0.2276584093290748</v>
+        <v>0.6221841238929925</v>
       </c>
       <c r="G5">
-        <v>-14.32509363443103</v>
+        <v>-10.30486879292505</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.90657951097264</v>
       </c>
       <c r="E6">
-        <v>-20.11120873931609</v>
+        <v>-13.73219194230727</v>
       </c>
       <c r="F6">
-        <v>0.4299763786866176</v>
+        <v>0.5360894146178316</v>
       </c>
       <c r="G6">
-        <v>-14.10567178630784</v>
+        <v>-10.0375870471358</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.37728941299045</v>
       </c>
       <c r="E7">
-        <v>-21.54418546888127</v>
+        <v>-16.22379004064555</v>
       </c>
       <c r="F7">
-        <v>0.6431964914324048</v>
+        <v>0.997325212863999</v>
       </c>
       <c r="G7">
-        <v>-13.47501444013945</v>
+        <v>-9.918262143905039</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.80797212319558</v>
       </c>
       <c r="E8">
-        <v>-21.75761697733678</v>
+        <v>-15.72130150780644</v>
       </c>
       <c r="F8">
-        <v>0.5121338576962726</v>
+        <v>0.9300468691434288</v>
       </c>
       <c r="G8">
-        <v>-12.62977504764805</v>
+        <v>-9.739369944484112</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.20352580751524</v>
       </c>
       <c r="E9">
-        <v>-22.24220445242358</v>
+        <v>-16.42802421839149</v>
       </c>
       <c r="F9">
-        <v>0.6394241062800559</v>
+        <v>0.7511874362657651</v>
       </c>
       <c r="G9">
-        <v>-12.13349684922515</v>
+        <v>-7.809722920033389</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.56609436439995</v>
       </c>
       <c r="E10">
-        <v>-23.21228509739871</v>
+        <v>-17.35273861075778</v>
       </c>
       <c r="F10">
-        <v>0.5093795360819643</v>
+        <v>1.042729686946245</v>
       </c>
       <c r="G10">
-        <v>-12.25977794216194</v>
+        <v>-8.298802118354862</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.89192633946142</v>
       </c>
       <c r="E11">
-        <v>-24.14176344442107</v>
+        <v>-17.64822606823227</v>
       </c>
       <c r="F11">
-        <v>0.8443257535669303</v>
+        <v>0.8908998824219297</v>
       </c>
       <c r="G11">
-        <v>-12.35538289473948</v>
+        <v>-8.373508970820298</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.19209569198273</v>
       </c>
       <c r="E12">
-        <v>-24.71521769343439</v>
+        <v>-17.92412334714959</v>
       </c>
       <c r="F12">
-        <v>0.5521357195774608</v>
+        <v>1.028403901082231</v>
       </c>
       <c r="G12">
-        <v>-11.17878934306756</v>
+        <v>-6.754455816743492</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.47283720642818</v>
       </c>
       <c r="E13">
-        <v>-24.77642001964805</v>
+        <v>-19.36333125694933</v>
       </c>
       <c r="F13">
-        <v>0.9326346889097744</v>
+        <v>1.589200349103468</v>
       </c>
       <c r="G13">
-        <v>-10.64543005980138</v>
+        <v>-6.521170807531652</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.76543690920385</v>
       </c>
       <c r="E14">
-        <v>-26.09612150038537</v>
+        <v>-20.53520070370625</v>
       </c>
       <c r="F14">
-        <v>0.9214020269278131</v>
+        <v>1.562207168915843</v>
       </c>
       <c r="G14">
-        <v>-10.0508399010144</v>
+        <v>-6.299255231023287</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-11.08354434707078</v>
       </c>
       <c r="E15">
-        <v>-26.61003537314584</v>
+        <v>-21.40819992290494</v>
       </c>
       <c r="F15">
-        <v>1.353670645465485</v>
+        <v>1.33247106689304</v>
       </c>
       <c r="G15">
-        <v>-9.918970887761878</v>
+        <v>-5.331294870987096</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.45589693779767</v>
       </c>
       <c r="E16">
-        <v>-28.58610746197693</v>
+        <v>-21.82702036997834</v>
       </c>
       <c r="F16">
-        <v>1.519852743610705</v>
+        <v>2.174133766507477</v>
       </c>
       <c r="G16">
-        <v>-9.282075939408982</v>
+        <v>-5.985196390682595</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.888541656665113</v>
       </c>
       <c r="E17">
-        <v>-29.00237837818401</v>
+        <v>-22.81927242369503</v>
       </c>
       <c r="F17">
-        <v>1.546821072776245</v>
+        <v>1.94404146650147</v>
       </c>
       <c r="G17">
-        <v>-9.834863335528633</v>
+        <v>-4.894390376682353</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.399536200840034</v>
       </c>
       <c r="E18">
-        <v>-28.98257536134847</v>
+        <v>-25.04717295209266</v>
       </c>
       <c r="F18">
-        <v>1.831078660516507</v>
+        <v>2.360034322308937</v>
       </c>
       <c r="G18">
-        <v>-9.203579276042385</v>
+        <v>-5.219595526660479</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.985486131964917</v>
       </c>
       <c r="E19">
-        <v>-30.05598219775661</v>
+        <v>-24.98244294462702</v>
       </c>
       <c r="F19">
-        <v>2.260149780879372</v>
+        <v>2.53066475340719</v>
       </c>
       <c r="G19">
-        <v>-9.299994690345109</v>
+        <v>-4.490662313565156</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.653341115986187</v>
       </c>
       <c r="E20">
-        <v>-31.82234065529248</v>
+        <v>-26.37077344895058</v>
       </c>
       <c r="F20">
-        <v>2.433979366887238</v>
+        <v>3.015499910591713</v>
       </c>
       <c r="G20">
-        <v>-8.820565564629963</v>
+        <v>-5.243095635469222</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.391797144888695</v>
       </c>
       <c r="E21">
-        <v>-31.68654983369847</v>
+        <v>-27.88755411850171</v>
       </c>
       <c r="F21">
-        <v>2.520326728220252</v>
+        <v>3.706255606968553</v>
       </c>
       <c r="G21">
-        <v>-8.758248604772989</v>
+        <v>-4.949094902521415</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.197878524045855</v>
       </c>
       <c r="E22">
-        <v>-31.22683726633581</v>
+        <v>-27.07395036438762</v>
       </c>
       <c r="F22">
-        <v>2.600144897684402</v>
+        <v>3.639389790214577</v>
       </c>
       <c r="G22">
-        <v>-8.131128415445676</v>
+        <v>-5.589212010445688</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.054299567204806</v>
       </c>
       <c r="E23">
-        <v>-31.65803403287217</v>
+        <v>-26.87372388613848</v>
       </c>
       <c r="F23">
-        <v>2.554747050541378</v>
+        <v>3.851721893104564</v>
       </c>
       <c r="G23">
-        <v>-8.537868639954445</v>
+        <v>-5.574088860278207</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.951768630511943</v>
       </c>
       <c r="E24">
-        <v>-32.76082613711609</v>
+        <v>-27.9115731446384</v>
       </c>
       <c r="F24">
-        <v>2.944482316414906</v>
+        <v>4.173116848247132</v>
       </c>
       <c r="G24">
-        <v>-8.683059412738313</v>
+        <v>-4.707029344416501</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.872809932761546</v>
       </c>
       <c r="E25">
-        <v>-33.19123268493811</v>
+        <v>-28.0767673479642</v>
       </c>
       <c r="F25">
-        <v>2.938441861313692</v>
+        <v>4.323891312700281</v>
       </c>
       <c r="G25">
-        <v>-8.170844321201196</v>
+        <v>-5.233452125306013</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.808140186037528</v>
       </c>
       <c r="E26">
-        <v>-32.50250386582254</v>
+        <v>-27.91548121770701</v>
       </c>
       <c r="F26">
-        <v>3.294734278401398</v>
+        <v>3.949389723364237</v>
       </c>
       <c r="G26">
-        <v>-8.707563575344247</v>
+        <v>-5.253572575908529</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.743890278138449</v>
       </c>
       <c r="E27">
-        <v>-32.64696445090423</v>
+        <v>-27.65423355220451</v>
       </c>
       <c r="F27">
-        <v>3.158833979032917</v>
+        <v>4.252905196484781</v>
       </c>
       <c r="G27">
-        <v>-8.459552443773617</v>
+        <v>-4.669059048530606</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.672318145888658</v>
       </c>
       <c r="E28">
-        <v>-33.13662834535363</v>
+        <v>-27.19742373668076</v>
       </c>
       <c r="F28">
-        <v>2.905492719499938</v>
+        <v>3.694540835158163</v>
       </c>
       <c r="G28">
-        <v>-8.26424757411235</v>
+        <v>-5.80062439674227</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.585831726713108</v>
       </c>
       <c r="E29">
-        <v>-31.91706727458493</v>
+        <v>-28.23940749194968</v>
       </c>
       <c r="F29">
-        <v>2.975637214434195</v>
+        <v>3.748815467389587</v>
       </c>
       <c r="G29">
-        <v>-8.778962956477763</v>
+        <v>-5.13550109931347</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.485656795539364</v>
       </c>
       <c r="E30">
-        <v>-31.2244688744298</v>
+        <v>-27.03233821673114</v>
       </c>
       <c r="F30">
-        <v>3.125545206584016</v>
+        <v>4.048242119009912</v>
       </c>
       <c r="G30">
-        <v>-8.029230079917122</v>
+        <v>-5.211129975037111</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.376902561121215</v>
       </c>
       <c r="E31">
-        <v>-31.97869527735531</v>
+        <v>-26.65137128388786</v>
       </c>
       <c r="F31">
-        <v>2.802155542735506</v>
+        <v>3.633854639229071</v>
       </c>
       <c r="G31">
-        <v>-8.552302733594441</v>
+        <v>-4.664573618658846</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.271894061915299</v>
       </c>
       <c r="E32">
-        <v>-30.9499980648249</v>
+        <v>-26.7560696029452</v>
       </c>
       <c r="F32">
-        <v>3.037531170036569</v>
+        <v>3.740566584792509</v>
       </c>
       <c r="G32">
-        <v>-8.662505840889951</v>
+        <v>-5.557272599786053</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.185199436135281</v>
       </c>
       <c r="E33">
-        <v>-30.5605832637203</v>
+        <v>-25.73171972546215</v>
       </c>
       <c r="F33">
-        <v>2.969058320521162</v>
+        <v>3.724042311841465</v>
       </c>
       <c r="G33">
-        <v>-7.95520244031449</v>
+        <v>-4.707341060464648</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.132794208513332</v>
       </c>
       <c r="E34">
-        <v>-30.73794321246772</v>
+        <v>-26.2064804119523</v>
       </c>
       <c r="F34">
-        <v>3.06888487623253</v>
+        <v>3.113769135585818</v>
       </c>
       <c r="G34">
-        <v>-8.260963071331345</v>
+        <v>-4.644951913733366</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.127578360623033</v>
       </c>
       <c r="E35">
-        <v>-30.42010547152836</v>
+        <v>-26.01509351496613</v>
       </c>
       <c r="F35">
-        <v>2.45698312966298</v>
+        <v>3.533479704297049</v>
       </c>
       <c r="G35">
-        <v>-8.557168785167098</v>
+        <v>-4.631443124573132</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.176618571660745</v>
       </c>
       <c r="E36">
-        <v>-30.01450590432036</v>
+        <v>-25.94778680579012</v>
       </c>
       <c r="F36">
-        <v>2.463565337045625</v>
+        <v>3.155225610626323</v>
       </c>
       <c r="G36">
-        <v>-7.386133622816874</v>
+        <v>-4.902117653454845</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.283132013055111</v>
       </c>
       <c r="E37">
-        <v>-28.80573845134894</v>
+        <v>-24.47429834775232</v>
       </c>
       <c r="F37">
-        <v>2.486752997384789</v>
+        <v>3.288009591825472</v>
       </c>
       <c r="G37">
-        <v>-8.717449895902853</v>
+        <v>-5.220366613726948</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.44200231456856</v>
       </c>
       <c r="E38">
-        <v>-29.04996811153061</v>
+        <v>-23.71123689203784</v>
       </c>
       <c r="F38">
-        <v>2.710324389195958</v>
+        <v>3.543009242898855</v>
       </c>
       <c r="G38">
-        <v>-8.710024491513829</v>
+        <v>-5.233360251102349</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.647710191052898</v>
       </c>
       <c r="E39">
-        <v>-28.49590025974413</v>
+        <v>-22.71184796328507</v>
       </c>
       <c r="F39">
-        <v>2.592295288175474</v>
+        <v>3.547054989294128</v>
       </c>
       <c r="G39">
-        <v>-8.360249554498584</v>
+        <v>-4.726263865197966</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.886462540597795</v>
       </c>
       <c r="E40">
-        <v>-28.21641642941274</v>
+        <v>-22.56817306844371</v>
       </c>
       <c r="F40">
-        <v>2.829465159271</v>
+        <v>3.194175445905955</v>
       </c>
       <c r="G40">
-        <v>-8.360055962426575</v>
+        <v>-5.117326413095705</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.147691096315592</v>
       </c>
       <c r="E41">
-        <v>-28.02493896294641</v>
+        <v>-21.58183067330704</v>
       </c>
       <c r="F41">
-        <v>2.486451471650169</v>
+        <v>3.111037179891385</v>
       </c>
       <c r="G41">
-        <v>-8.670928736633046</v>
+        <v>-4.703531562234133</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.412078129592786</v>
       </c>
       <c r="E42">
-        <v>-26.57028442830651</v>
+        <v>-22.8475391584509</v>
       </c>
       <c r="F42">
-        <v>2.609124400330748</v>
+        <v>3.107983817644667</v>
       </c>
       <c r="G42">
-        <v>-8.472457488166913</v>
+        <v>-4.765421963288379</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.666856619224189</v>
       </c>
       <c r="E43">
-        <v>-26.16632643292629</v>
+        <v>-20.5340504713083</v>
       </c>
       <c r="F43">
-        <v>2.693172213753592</v>
+        <v>3.554061320787006</v>
       </c>
       <c r="G43">
-        <v>-8.594141589698921</v>
+        <v>-4.341038610454477</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.893417041400552</v>
       </c>
       <c r="E44">
-        <v>-25.90471648950317</v>
+        <v>-21.11241358614594</v>
       </c>
       <c r="F44">
-        <v>2.871042575952313</v>
+        <v>3.439960337990597</v>
       </c>
       <c r="G44">
-        <v>-8.515786018859382</v>
+        <v>-3.875672800343112</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.083168592058408</v>
       </c>
       <c r="E45">
-        <v>-25.37275211934812</v>
+        <v>-20.48845779499907</v>
       </c>
       <c r="F45">
-        <v>2.816367013897934</v>
+        <v>3.542136143656304</v>
       </c>
       <c r="G45">
-        <v>-8.88315814709793</v>
+        <v>-4.415722494368999</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.221930921878236</v>
       </c>
       <c r="E46">
-        <v>-25.39527674906228</v>
+        <v>-19.30066623363119</v>
       </c>
       <c r="F46">
-        <v>3.053588243772434</v>
+        <v>2.994674754085334</v>
       </c>
       <c r="G46">
-        <v>-8.504902206946703</v>
+        <v>-4.75761593719846</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.308658128861051</v>
       </c>
       <c r="E47">
-        <v>-24.48008573753412</v>
+        <v>-18.83853546114843</v>
       </c>
       <c r="F47">
-        <v>2.465109413884443</v>
+        <v>3.109619014897793</v>
       </c>
       <c r="G47">
-        <v>-8.830816100781668</v>
+        <v>-4.687253422077728</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.3425857436238</v>
       </c>
       <c r="E48">
-        <v>-23.65416453411917</v>
+        <v>-18.25513668321426</v>
       </c>
       <c r="F48">
-        <v>2.917711138691231</v>
+        <v>3.220895264850656</v>
       </c>
       <c r="G48">
-        <v>-9.102986866694488</v>
+        <v>-5.158381057247478</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.335058637346116</v>
       </c>
       <c r="E49">
-        <v>-23.07774413463083</v>
+        <v>-19.3355626543343</v>
       </c>
       <c r="F49">
-        <v>2.645595760341205</v>
+        <v>3.518229460411511</v>
       </c>
       <c r="G49">
-        <v>-8.841880379880116</v>
+        <v>-5.212029029744399</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.292742964465956</v>
       </c>
       <c r="E50">
-        <v>-22.81817653298517</v>
+        <v>-18.2082262209688</v>
       </c>
       <c r="F50">
-        <v>3.057435181991035</v>
+        <v>2.871301026581986</v>
       </c>
       <c r="G50">
-        <v>-9.060928168745527</v>
+        <v>-5.348967530306265</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.2283223266744</v>
       </c>
       <c r="E51">
-        <v>-22.42708846073474</v>
+        <v>-17.75659697970983</v>
       </c>
       <c r="F51">
-        <v>2.817051245372646</v>
+        <v>3.150447587446975</v>
       </c>
       <c r="G51">
-        <v>-9.082846728762616</v>
+        <v>-4.667779372122423</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.150051505459405</v>
       </c>
       <c r="E52">
-        <v>-21.81296851513254</v>
+        <v>-15.46364492219202</v>
       </c>
       <c r="F52">
-        <v>2.747178454946508</v>
+        <v>3.520656576901713</v>
       </c>
       <c r="G52">
-        <v>-8.530525266104407</v>
+        <v>-5.575296349812083</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.06726687022025</v>
       </c>
       <c r="E53">
-        <v>-21.77299567506683</v>
+        <v>-16.10357716963794</v>
       </c>
       <c r="F53">
-        <v>3.081673212196949</v>
+        <v>3.275830934269514</v>
       </c>
       <c r="G53">
-        <v>-9.661162028614749</v>
+        <v>-5.278519703424987</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.986848556416106</v>
       </c>
       <c r="E54">
-        <v>-21.43692403353559</v>
+        <v>-15.18423354744475</v>
       </c>
       <c r="F54">
-        <v>2.936235090552634</v>
+        <v>3.152882987611205</v>
       </c>
       <c r="G54">
-        <v>-9.410050142670444</v>
+        <v>-5.474694096799508</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.912378619506603</v>
       </c>
       <c r="E55">
-        <v>-20.38983668806003</v>
+        <v>-15.74757118552493</v>
       </c>
       <c r="F55">
-        <v>2.692966778637698</v>
+        <v>3.112246596299473</v>
       </c>
       <c r="G55">
-        <v>-9.64331218333137</v>
+        <v>-6.29013671630959</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.847254023948565</v>
       </c>
       <c r="E56">
-        <v>-20.99572386791629</v>
+        <v>-14.48628249101255</v>
       </c>
       <c r="F56">
-        <v>2.913799587815212</v>
+        <v>3.224588126732336</v>
       </c>
       <c r="G56">
-        <v>-9.538539497716739</v>
+        <v>-6.714995846269611</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.78791212575347</v>
       </c>
       <c r="E57">
-        <v>-20.06649005849034</v>
+        <v>-15.37941077717534</v>
       </c>
       <c r="F57">
-        <v>2.869120763577818</v>
+        <v>3.312754582881899</v>
       </c>
       <c r="G57">
-        <v>-9.751064218121973</v>
+        <v>-6.183339516992783</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.73500091058914</v>
       </c>
       <c r="E58">
-        <v>-18.86407152607768</v>
+        <v>-15.04796270760593</v>
       </c>
       <c r="F58">
-        <v>3.181527932400012</v>
+        <v>3.261046232864348</v>
       </c>
       <c r="G58">
-        <v>-10.12548112904865</v>
+        <v>-5.780750037756714</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.681164236731714</v>
       </c>
       <c r="E59">
-        <v>-19.77005162147423</v>
+        <v>-14.33058902615484</v>
       </c>
       <c r="F59">
-        <v>3.019840555782382</v>
+        <v>3.134728487611451</v>
       </c>
       <c r="G59">
-        <v>-10.41584626850859</v>
+        <v>-5.730954219370581</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.625842350334311</v>
       </c>
       <c r="E60">
-        <v>-18.56169173116351</v>
+        <v>-12.56480568481794</v>
       </c>
       <c r="F60">
-        <v>2.847218729447799</v>
+        <v>3.439380480808637</v>
       </c>
       <c r="G60">
-        <v>-10.26394539763566</v>
+        <v>-5.862632921772657</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.559700385708203</v>
       </c>
       <c r="E61">
-        <v>-19.39942772326447</v>
+        <v>-13.52134619251014</v>
       </c>
       <c r="F61">
-        <v>2.995763228852612</v>
+        <v>2.913799587815212</v>
       </c>
       <c r="G61">
-        <v>-10.58590213826993</v>
+        <v>-6.084354906209015</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.482005694023671</v>
       </c>
       <c r="E62">
-        <v>-18.07180594148774</v>
+        <v>-11.61981731431932</v>
       </c>
       <c r="F62">
-        <v>2.830530439751</v>
+        <v>3.747574573020193</v>
       </c>
       <c r="G62">
-        <v>-11.05285934083763</v>
+        <v>-6.32925872096285</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.385571712550862</v>
       </c>
       <c r="E63">
-        <v>-16.86208750897471</v>
+        <v>-13.00615981855351</v>
       </c>
       <c r="F63">
-        <v>2.891599341420185</v>
+        <v>3.237883423547268</v>
       </c>
       <c r="G63">
-        <v>-11.0796177026549</v>
+        <v>-6.932744271397481</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.272701543089566</v>
       </c>
       <c r="E64">
-        <v>-17.6787072267779</v>
+        <v>-13.60007371313349</v>
       </c>
       <c r="F64">
-        <v>2.865456066187833</v>
+        <v>3.599745783051399</v>
       </c>
       <c r="G64">
-        <v>-10.80158667503691</v>
+        <v>-7.50971427041024</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.140138152507991</v>
       </c>
       <c r="E65">
-        <v>-17.52421833600623</v>
+        <v>-11.90834903571803</v>
       </c>
       <c r="F65">
-        <v>2.877828561716046</v>
+        <v>3.318226777944792</v>
       </c>
       <c r="G65">
-        <v>-11.63367493151806</v>
+        <v>-7.523885866325482</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.992249816018169</v>
       </c>
       <c r="E66">
-        <v>-18.38636280300853</v>
+        <v>-11.95457116991433</v>
       </c>
       <c r="F66">
-        <v>2.916341019007001</v>
+        <v>3.614333333014698</v>
       </c>
       <c r="G66">
-        <v>-11.51471096265883</v>
+        <v>-7.453910535348763</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.828814384472653</v>
       </c>
       <c r="E67">
-        <v>-18.01855108715753</v>
+        <v>-12.78485329379866</v>
       </c>
       <c r="F67">
-        <v>2.513688191854217</v>
+        <v>3.185305287756778</v>
       </c>
       <c r="G67">
-        <v>-11.50219638363111</v>
+        <v>-6.908446825749793</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.65378818024803</v>
       </c>
       <c r="E68">
-        <v>-17.82140849970761</v>
+        <v>-13.40649956320161</v>
       </c>
       <c r="F68">
-        <v>2.481608835813403</v>
+        <v>3.110059706356082</v>
       </c>
       <c r="G68">
-        <v>-11.60482643156742</v>
+        <v>-6.865633446842158</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.4677355128814</v>
       </c>
       <c r="E69">
-        <v>-17.88853859839732</v>
+        <v>-11.19017381436758</v>
       </c>
       <c r="F69">
-        <v>2.526410258426412</v>
+        <v>2.991854991446204</v>
       </c>
       <c r="G69">
-        <v>-11.42305003839574</v>
+        <v>-7.161245259575652</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.272031273803417</v>
       </c>
       <c r="E70">
-        <v>-17.42766674168869</v>
+        <v>-11.97398926645922</v>
       </c>
       <c r="F70">
-        <v>2.271317830203916</v>
+        <v>2.65511038832976</v>
       </c>
       <c r="G70">
-        <v>-11.14254825094349</v>
+        <v>-8.103274125627552</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.068089573419928</v>
       </c>
       <c r="E71">
-        <v>-17.50381756060168</v>
+        <v>-11.87476587247715</v>
       </c>
       <c r="F71">
-        <v>2.126638493100565</v>
+        <v>2.825928030461046</v>
       </c>
       <c r="G71">
-        <v>-10.98951863985411</v>
+        <v>-7.386268152900811</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.85470700313686</v>
       </c>
       <c r="E72">
-        <v>-16.67524267141823</v>
+        <v>-12.11325795609111</v>
       </c>
       <c r="F72">
-        <v>2.065821415121831</v>
+        <v>2.987353642979391</v>
       </c>
       <c r="G72">
-        <v>-10.92862244893237</v>
+        <v>-7.280931097177957</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.634752238596128</v>
       </c>
       <c r="E73">
-        <v>-17.19499827564859</v>
+        <v>-12.81778435678244</v>
       </c>
       <c r="F73">
-        <v>1.714192706511886</v>
+        <v>2.72312266556921</v>
       </c>
       <c r="G73">
-        <v>-11.4546317959054</v>
+        <v>-6.717345200906173</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.404988688254341</v>
       </c>
       <c r="E74">
-        <v>-17.6183698390997</v>
+        <v>-13.9830648738582</v>
       </c>
       <c r="F74">
-        <v>2.072865851515238</v>
+        <v>2.103734134413159</v>
       </c>
       <c r="G74">
-        <v>-11.30087047240826</v>
+        <v>-5.965486092775011</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.169923711208633</v>
       </c>
       <c r="E75">
-        <v>-17.56823057488678</v>
+        <v>-12.13035294547007</v>
       </c>
       <c r="F75">
-        <v>1.80035948375109</v>
+        <v>2.410778452669629</v>
       </c>
       <c r="G75">
-        <v>-10.69569181164895</v>
+        <v>-6.951132237016609</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.925835929603683</v>
       </c>
       <c r="E76">
-        <v>-17.68376100377046</v>
+        <v>-13.26037929239611</v>
       </c>
       <c r="F76">
-        <v>1.749081884782995</v>
+        <v>1.991993998714728</v>
       </c>
       <c r="G76">
-        <v>-10.46317460828202</v>
+        <v>-6.724439201917693</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.677790483851425</v>
       </c>
       <c r="E77">
-        <v>-19.32164665370872</v>
+        <v>-13.2115487571714</v>
       </c>
       <c r="F77">
-        <v>1.590724545124619</v>
+        <v>2.590900317469159</v>
       </c>
       <c r="G77">
-        <v>-10.40105452171862</v>
+        <v>-5.485696032688327</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.421925204618503</v>
       </c>
       <c r="E78">
-        <v>-18.83167935150081</v>
+        <v>-13.88279540238036</v>
       </c>
       <c r="F78">
-        <v>1.657252387978253</v>
+        <v>2.17295085785628</v>
       </c>
       <c r="G78">
-        <v>-10.48928000700896</v>
+        <v>-6.163225628833387</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.162439823127249</v>
       </c>
       <c r="E79">
-        <v>-18.94408966179321</v>
+        <v>-13.39678145798115</v>
       </c>
       <c r="F79">
-        <v>1.244718794444877</v>
+        <v>2.032728137379991</v>
       </c>
       <c r="G79">
-        <v>-10.00649419163851</v>
+        <v>-5.581346922367699</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.895742157852163</v>
       </c>
       <c r="E80">
-        <v>-19.56333131149809</v>
+        <v>-13.22333184653936</v>
       </c>
       <c r="F80">
-        <v>1.0001068706026</v>
+        <v>2.119367084038791</v>
       </c>
       <c r="G80">
-        <v>-9.433481345826438</v>
+        <v>-5.334969839133674</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.62609523155669</v>
       </c>
       <c r="E81">
-        <v>-19.95081471843841</v>
+        <v>-13.89714160803666</v>
       </c>
       <c r="F81">
-        <v>1.305204525462491</v>
+        <v>1.959074678127475</v>
       </c>
       <c r="G81">
-        <v>-9.187780194233659</v>
+        <v>-5.067169660338034</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.351927855947394</v>
       </c>
       <c r="E82">
-        <v>-20.48487577205901</v>
+        <v>-15.4035339582142</v>
       </c>
       <c r="F82">
-        <v>1.450218522996573</v>
+        <v>1.656008180139248</v>
       </c>
       <c r="G82">
-        <v>-8.734016783556489</v>
+        <v>-4.689592933049611</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.078136914257239</v>
       </c>
       <c r="E83">
-        <v>-21.50614628721684</v>
+        <v>-15.68718398463265</v>
       </c>
       <c r="F83">
-        <v>1.070355739829609</v>
+        <v>2.042315661699992</v>
       </c>
       <c r="G83">
-        <v>-8.838159474631706</v>
+        <v>-4.838734296591052</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.80517664748356</v>
       </c>
       <c r="E84">
-        <v>-21.26112867255783</v>
+        <v>-16.82706881947339</v>
       </c>
       <c r="F84">
-        <v>0.7712935698665148</v>
+        <v>1.319336473354251</v>
       </c>
       <c r="G84">
-        <v>-8.344821250726074</v>
+        <v>-4.726877453629582</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.53738781630758</v>
       </c>
       <c r="E85">
-        <v>-22.4407055820758</v>
+        <v>-15.90000414909712</v>
       </c>
       <c r="F85">
-        <v>0.8073905078109059</v>
+        <v>0.9558289761881605</v>
       </c>
       <c r="G85">
-        <v>-7.803002978279646</v>
+        <v>-4.572039889460945</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.276420068311872</v>
       </c>
       <c r="E86">
-        <v>-23.00509835459978</v>
+        <v>-18.09146404715503</v>
       </c>
       <c r="F86">
-        <v>0.7899003584681972</v>
+        <v>0.4891557743100171</v>
       </c>
       <c r="G86">
-        <v>-8.039792332116974</v>
+        <v>-4.025165254591413</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.024498762108296</v>
       </c>
       <c r="E87">
-        <v>-24.62768229086612</v>
+        <v>-18.99760716761586</v>
       </c>
       <c r="F87">
-        <v>0.3432695059007878</v>
+        <v>0.5150637931999744</v>
       </c>
       <c r="G87">
-        <v>-7.889456603927895</v>
+        <v>-3.403301582202332</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.782533418647811</v>
       </c>
       <c r="E88">
-        <v>-25.41787383436055</v>
+        <v>-21.42735989643139</v>
       </c>
       <c r="F88">
-        <v>0.4136832202409542</v>
+        <v>0.438841566631378</v>
       </c>
       <c r="G88">
-        <v>-6.957858741213471</v>
+        <v>-3.319102155765421</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.55065768393378</v>
       </c>
       <c r="E89">
-        <v>-27.69192856984436</v>
+        <v>-21.94093413364129</v>
       </c>
       <c r="F89">
-        <v>0.3405317516345354</v>
+        <v>0.2079664594297249</v>
       </c>
       <c r="G89">
-        <v>-6.978349969852203</v>
+        <v>-2.815647925792021</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.330832335018295</v>
       </c>
       <c r="E90">
-        <v>-27.7299768084568</v>
+        <v>-23.86078521766715</v>
       </c>
       <c r="F90">
-        <v>-0.1535836055635501</v>
+        <v>0.1383844259619693</v>
       </c>
       <c r="G90">
-        <v>-6.64143085890686</v>
+        <v>-2.521607818185502</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.123866494571069</v>
       </c>
       <c r="E91">
-        <v>-29.78538776190227</v>
+        <v>-24.82297726092091</v>
       </c>
       <c r="F91">
-        <v>-0.5778742176448597</v>
+        <v>-0.3288429537086471</v>
       </c>
       <c r="G91">
-        <v>-6.654831367755632</v>
+        <v>-2.180521555859664</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.934754738108629</v>
       </c>
       <c r="E92">
-        <v>-31.57524899953795</v>
+        <v>-27.23031404339847</v>
       </c>
       <c r="F92">
-        <v>-0.5816151248359023</v>
+        <v>-0.3694992258380468</v>
       </c>
       <c r="G92">
-        <v>-6.614987494359295</v>
+        <v>-2.561523878456147</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.766102143206183</v>
       </c>
       <c r="E93">
-        <v>-32.43712855081081</v>
+        <v>-28.42075476206085</v>
       </c>
       <c r="F93">
-        <v>-1.003256617963059</v>
+        <v>-1.109186584698254</v>
       </c>
       <c r="G93">
-        <v>-6.047503506874891</v>
+        <v>-3.158049957963196</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.625351554306044</v>
       </c>
       <c r="E94">
-        <v>-34.94521935148503</v>
+        <v>-29.51979502558941</v>
       </c>
       <c r="F94">
-        <v>-1.359494362802181</v>
+        <v>-1.188263365336898</v>
       </c>
       <c r="G94">
-        <v>-6.238457476748335</v>
+        <v>-2.335503493776916</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.514012395611416</v>
       </c>
       <c r="E95">
-        <v>-36.90099029133972</v>
+        <v>-33.12453052704213</v>
       </c>
       <c r="F95">
-        <v>-1.411430513855501</v>
+        <v>-1.581579663492728</v>
       </c>
       <c r="G95">
-        <v>-6.580357482020916</v>
+        <v>-2.669302163019227</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.439352101297686</v>
       </c>
       <c r="E96">
-        <v>-38.55951219733094</v>
+        <v>-34.78393095699084</v>
       </c>
       <c r="F96">
-        <v>-1.717787287167648</v>
+        <v>-2.025654174255098</v>
       </c>
       <c r="G96">
-        <v>-5.929241719429385</v>
+        <v>-2.965471783417826</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.3969099906211</v>
       </c>
       <c r="E97">
-        <v>-40.25363696597046</v>
+        <v>-36.72091552242471</v>
       </c>
       <c r="F97">
-        <v>-2.089167588129945</v>
+        <v>-1.997370397653912</v>
       </c>
       <c r="G97">
-        <v>-6.626150210104526</v>
+        <v>-2.770301443840495</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.393134576099468</v>
       </c>
       <c r="E98">
-        <v>-42.42921776992047</v>
+        <v>-39.34762969972986</v>
       </c>
       <c r="F98">
-        <v>-2.627545929129219</v>
+        <v>-2.757378437272194</v>
       </c>
       <c r="G98">
-        <v>-6.741990456039162</v>
+        <v>-2.857109441417164</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.413365067764058</v>
       </c>
       <c r="E99">
-        <v>-44.70791871973615</v>
+        <v>-41.35691814540721</v>
       </c>
       <c r="F99">
-        <v>-2.674501106989506</v>
+        <v>-3.130308613645129</v>
       </c>
       <c r="G99">
-        <v>-6.614298437831811</v>
+        <v>-3.149951903154486</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.468913031344049</v>
       </c>
       <c r="E100">
-        <v>-46.60921438151558</v>
+        <v>-44.05584336923866</v>
       </c>
       <c r="F100">
-        <v>-3.102409199518841</v>
+        <v>-3.959373501797792</v>
       </c>
       <c r="G100">
-        <v>-7.055550550702819</v>
+        <v>-3.561945363379925</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.529781676650698</v>
       </c>
       <c r="E101">
-        <v>-48.63937116753877</v>
+        <v>-46.14541260212398</v>
       </c>
       <c r="F101">
-        <v>-3.317402018506619</v>
+        <v>-3.663752370025926</v>
       </c>
       <c r="G101">
-        <v>-7.041907231458647</v>
+        <v>-2.927964139771813</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.631437513236226</v>
       </c>
       <c r="E102">
-        <v>-50.83062275579233</v>
+        <v>-48.02268470929272</v>
       </c>
       <c r="F102">
-        <v>-3.419467651307755</v>
+        <v>-3.599205153632386</v>
       </c>
       <c r="G102">
-        <v>-7.551067505723921</v>
+        <v>-3.11802233615953</v>
       </c>
     </row>
   </sheetData>
